--- a/public/fixtures/sample.xlsx
+++ b/public/fixtures/sample.xlsx
@@ -9,10 +9,10 @@
     <sheet name="culture" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">vocabulary!$A$1:$F$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">sentences!$A$1:$D$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">grammar!$A$1:$F$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3">culture!$A$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">vocabulary!$A$1:$G$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">sentences!$A$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">grammar!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3">culture!$A$1:$F$5</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -406,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G14"/>
   <cols>
     <col min="1" max="1" width="24.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -435,6 +435,9 @@
       <c r="F1" t="str">
         <v>characters</v>
       </c>
+      <c r="G1" t="str">
+        <v>exam_tags</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -475,6 +478,9 @@
       <c r="F3" t="str">
         <v>[{"char":"好","traditional":"好","decomposition":{"type":"layout","layout":"left-right","children":[{"type":"character","value":"女"},{"type":"character","value":"子"}]}}]</v>
       </c>
+      <c r="G3" t="str">
+        <v>["2026-midterm","2026-final"]</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -495,6 +501,9 @@
       <c r="F4" t="str">
         <v>[{"char":"你","traditional":"你","decomposition":{"type":"layout","layout":"left-right","children":[{"type":"character","value":"亻"},{"type":"character","value":"尔"}]}}]</v>
       </c>
+      <c r="G4" t="str">
+        <v>["2026-midterm"]</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -595,6 +604,9 @@
       <c r="F9" t="str">
         <v>[{"char":"学","traditional":"學","decomposition":{"type":"layout","layout":"top-bottom","children":[{"type":"layout","layout":"top-bottom","children":[{"type":"character","value":"⺍"},{"type":"character","value":"冖"}]},{"type":"character","value":"子"}]}},{"char":"校","traditional":"校","decomposition":{"type":"layout","layout":"left-right","children":[{"type":"character","value":"木"},{"type":"character","value":"交"}]}}]</v>
       </c>
+      <c r="G9" t="str">
+        <v>["2026-final"]</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -697,21 +709,22 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F14"/>
+  <autoFilter ref="A1:G14"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G14"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <cols>
     <col min="1" max="1" width="24.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
     <col min="3" max="3" width="24.83203125" customWidth="1"/>
     <col min="4" max="4" width="60.83203125" customWidth="1"/>
+    <col min="5" max="5" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -727,6 +740,9 @@
       <c r="D1" t="str">
         <v>explanation</v>
       </c>
+      <c r="E1" t="str">
+        <v>exam_tags</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -741,6 +757,9 @@
       <c r="D2" t="str">
         <v>평서문 끝에 吗를 붙여 예/아니요 의문문을 만듭니다.</v>
       </c>
+      <c r="E2" t="str">
+        <v>["2026-midterm"]</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -785,16 +804,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D5"/>
+  <autoFilter ref="A1:E5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <cols>
     <col min="1" max="1" width="24.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -802,6 +821,7 @@
     <col min="4" max="4" width="24.83203125" customWidth="1"/>
     <col min="5" max="5" width="24.83203125" customWidth="1"/>
     <col min="6" max="6" width="90.83203125" customWidth="1"/>
+    <col min="7" max="7" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -823,6 +843,9 @@
       <c r="F1" t="str">
         <v>questions</v>
       </c>
+      <c r="G1" t="str">
+        <v>exam_tags</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -843,6 +866,9 @@
       <c r="F2" t="str">
         <v>[{"type":"error","prompt":"你叫什么名字吗？에서 불필요한 부분은?","options":["你","叫","什么","吗"],"answer":"吗"},{"type":"blank","prompt":"你___什么名字？","options":["叫","是","吗","不"],"answer":"叫"},{"type":"order","prompt":"너는 학생이니? — 문장을 배열하세요.","tokens":["你","是","学生","吗"],"answer":"你是学生吗？"}]</v>
       </c>
+      <c r="G2" t="str">
+        <v>["2026-midterm"]</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -885,22 +911,23 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F4"/>
+  <autoFilter ref="A1:G4"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <cols>
     <col min="1" max="1" width="24.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
     <col min="3" max="3" width="24.83203125" customWidth="1"/>
     <col min="4" max="4" width="24.83203125" customWidth="1"/>
     <col min="5" max="5" width="60.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -919,6 +946,9 @@
       <c r="E1" t="str">
         <v>explanation</v>
       </c>
+      <c r="F1" t="str">
+        <v>exam_tags</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -936,6 +966,9 @@
       <c r="E2" t="str">
         <v>춘절(春节)은 음력 새해를 맞이하는 명절입니다.</v>
       </c>
+      <c r="F2" t="str">
+        <v>["2026-midterm"]</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -989,9 +1022,9 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E5"/>
+  <autoFilter ref="A1:F5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
   </ignoredErrors>
 </worksheet>
 </file>